--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto.xlsx
@@ -759,7 +759,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.9762240648583298</v>
+        <v>0.9762240648583299</v>
       </c>
       <c r="C24">
         <v>0.981496078599621</v>
@@ -776,7 +776,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.9762240648583299</v>
+        <v>0.97622406485833</v>
       </c>
       <c r="C25">
         <v>0.981496078599621</v>
@@ -793,7 +793,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0.9762240648583298</v>
+        <v>0.97622406485833</v>
       </c>
       <c r="C26">
         <v>0.981496078599621</v>
@@ -4771,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="B260">
-        <v>0.5237220232685109</v>
+        <v>0.523722023268511</v>
       </c>
       <c r="C260">
         <v>0.6436762602045494</v>
